--- a/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>DOO</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2467800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2778000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2429400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3076300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2709300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2438500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1809300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2347500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1588000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1903800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1808600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1815100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1674700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1233300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1229800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1615900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1643600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1459500</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1840400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2080400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1805900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2288700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2054600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1835800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1354900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1738000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1177400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1333700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1266600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1313200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1187800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>984900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>994700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1232200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1201700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1131700</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>627400</v>
+      </c>
+      <c r="E10" s="3">
         <v>697600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>623500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>787600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>654700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>602700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>454400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>609500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>410600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>570100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>542000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>501900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>486900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>248400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>235100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>383700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>441900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>327800</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>114400</v>
+      </c>
+      <c r="E12" s="3">
         <v>102700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>101700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>121000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>80600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>82100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>84000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>85100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>68300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>65800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>78900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>66000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>46900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>50500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>64700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>60300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1056,11 +1076,11 @@
       <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>91</v>
@@ -1068,41 +1088,44 @@
       <c r="I14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K14" s="3">
         <v>-8600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>29300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>177100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-40400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2150000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2399200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2147500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2639400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2324500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2092700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1609700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1402500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1565400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1492100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1566000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1390400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1173800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1357100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1418500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1435600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1349600</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>317800</v>
+      </c>
+      <c r="E18" s="3">
         <v>378800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>281900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>436900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>384800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>345800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>199600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>346600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>185500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>338400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>316500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>249100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>284300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>59500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-127300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>197400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>208000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1310,288 +1343,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-158100</v>
+      </c>
+      <c r="E20" s="3">
         <v>80000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-44100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>59000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-134700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-45300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>101000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>93200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-86800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-13900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E21" s="3">
         <v>554500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>330200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>585900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>326400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>417800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>255800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>375800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>261200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>378000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>391200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>418100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>358100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>217000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-150200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>246700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>265200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>190100</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E22" s="3">
         <v>44100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>42100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18600</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E23" s="3">
         <v>414700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>195700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>457100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>219400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>319700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>169700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>288800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>179600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>298200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>310100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>324900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>267700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>126200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-234500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>163300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>184200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>114800</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E24" s="3">
         <v>76000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>92000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>77800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>82000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>48700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>79200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>85300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>60700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>69000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-8400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>45100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>48900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E26" s="3">
         <v>338700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>154500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>365100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>141600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>237700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>121000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>209600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>127700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>212900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>244400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>264200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>198700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>126100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-226100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>118200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>135300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E27" s="3">
         <v>337700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>154200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>365300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>141200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>236500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>120900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>209400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>127600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>212600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>244200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>264300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>198800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>126300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-226000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>118400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>135600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>158100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-80000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>44100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-59000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>134700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>45300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-101000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-93200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>86800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>13900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E33" s="3">
         <v>337700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>154200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>365300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>141200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>236500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>120900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>209400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>127600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>212600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>244200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>264300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>198800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>126300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-226000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>118400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>135600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E35" s="3">
         <v>337700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>154200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>365300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>141200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>236500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>120900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>209400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>127600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>212600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>244200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>264300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>198800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>126300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-226000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>118400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>135600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2311,512 +2397,540 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>283600</v>
+      </c>
+      <c r="E41" s="3">
         <v>388500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>213000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>202300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>265800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>34300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>355400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>690900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1325700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1309300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1086100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>800700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>42500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>123900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>270400</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>133000</v>
+      </c>
+      <c r="E42" s="3">
         <v>141100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>125400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>122600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>85500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>114400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>94600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>73600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>74400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>72500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>93300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>76500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>13400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>19100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>590400</v>
+      </c>
+      <c r="E43" s="3">
         <v>541200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>650800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>698900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>555300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>410000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>447400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>497300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>496400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>323400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>295700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>339900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>226900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>310400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>417500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>387100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2586200</v>
+      </c>
+      <c r="E44" s="3">
         <v>2352600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2503000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2290100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2474800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2178000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2001500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1691300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1745300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1340600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1276900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1087300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1066500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>916200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1116500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1166300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1252300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1075600</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E45" s="3">
         <v>75000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>56600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>66700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>72400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>123000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>168700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>140100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>58500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>44000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>31000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3653000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3498400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3548800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3380600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3247900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2884500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2767500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2668100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2408900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2135900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2395200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2862300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2747300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2270500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2269800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1672200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1798400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1687100</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E47" s="3">
         <v>101700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>85900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>90800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>163500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>119300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>127100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>77600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>69400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>59100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>61400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>43700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>42400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>34000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>32300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>32100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2098600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2033700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2047400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1990700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1758500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1621900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1591100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1574600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1407200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1366500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1296200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1278500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1226500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1212300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1229800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1242100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1149000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1088600</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>735400</v>
+      </c>
+      <c r="E49" s="3">
         <v>733400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>738700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>741300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>735400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>515200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>505400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>494900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>480300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>466100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>464200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>465100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>460800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>466600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>472600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>610100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>607000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>490400</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2927,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>315900</v>
+      </c>
+      <c r="E52" s="3">
         <v>289300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>290900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>261200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>245700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>238400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>219600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>215700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>206800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>225600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>212600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>229600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>245500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>248200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>230600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>210400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>218200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>205200</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>6889800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6656500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6711700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6464600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6151000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5379300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5210700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5030900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4572600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4253200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4429600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4885900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4723800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4240000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4236800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3767100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3804700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3505300</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3139,344 +3269,363 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1525900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1379500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1603400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1548200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1858400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1571400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1447200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1622900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1419900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1224000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1273200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1296500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1183600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>747800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>957000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1085800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1178200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1028400</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E58" s="3">
         <v>136900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>136500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>133100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>450100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>316000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>459900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>132500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>119000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>60400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>54600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>58800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>90800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>59200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>52000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>49500</v>
-      </c>
-      <c r="S58" s="3">
-        <v>48500</v>
       </c>
       <c r="T58" s="3">
         <v>48500</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>951700</v>
+      </c>
+      <c r="E59" s="3">
         <v>987700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>912700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>802000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>803900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>795800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1029100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>864000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>617500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>683100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>687900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>837200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>591600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>703700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1455700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>748800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>712100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>656200</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2617600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2504100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2652600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2483300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3112400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2683200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2936200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2619400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2156400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1967500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2015700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2192500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1866000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1510700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2464700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1884100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1938800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1733100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2963200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2813500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2923800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2883000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2405600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2264800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2060800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2054900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2176600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2203100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2162900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2590700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2695500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2744300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1942400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1836800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1807900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1809000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>602100</v>
+      </c>
+      <c r="E62" s="3">
         <v>557400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>557700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>558200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>463200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>422100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>425700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>489400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>466400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>501500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>577600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>609000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>651000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>623300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>635900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>616400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>577800</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>6188200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5880200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6138800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5929700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5984900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5373800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5425600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5166500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4802200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4673900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4683900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5364600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5174400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4910100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5034500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4360900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4367500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4124600</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E72" s="3">
         <v>443600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>263200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>175500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-129300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-299300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-293600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-404300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-555700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-692000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-551900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-575900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-724400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-932300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-757000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-798800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-851900</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>701600</v>
+      </c>
+      <c r="E76" s="3">
         <v>776300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>572900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>534900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>166100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-214900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-135600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-229600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-420700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-254300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-478700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-450600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-670100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-797700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-593800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-562800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-619300</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E81" s="3">
         <v>337700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>154200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>365300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>141200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>236500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>120900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>209400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>127600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>212600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>244200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>264300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>198800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>126300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-226000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>118400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>135600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E83" s="3">
         <v>95700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>92400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>90000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>76300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>72800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>74500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>65900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>65800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>68000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>64300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>63900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>63200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>59400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>56700</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>305000</v>
+      </c>
+      <c r="E89" s="3">
         <v>489400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>258800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>307200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>343300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>332100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-333100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>708800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-265700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>162000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>164900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>318600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>309000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>113900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>212700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>138800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>170500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-138300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-102600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-117800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-262900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-175500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-112000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-109000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-333000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-135800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-131700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-85500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-107000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-34900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-116200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-56200</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-137000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-99900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-115600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-253900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-377000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-115000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-107500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-328900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-130800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-131000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-97000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-119800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-61700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-43600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-126200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-197400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5080,19 +5313,20 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E96" s="3">
         <v>-13900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-14200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-12600</v>
       </c>
       <c r="G96" s="3">
         <v>-12600</v>
@@ -5101,26 +5335,26 @@
         <v>-12600</v>
       </c>
       <c r="I96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="J96" s="3">
         <v>-13000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-10700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-10500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-10900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-11000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-9600</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5128,16 +5362,19 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
-        <v>-8900</v>
+        <v>0</v>
       </c>
       <c r="S96" s="3">
         <v>-8900</v>
       </c>
       <c r="T96" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="U96" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-236000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-240400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-115300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>109700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>72800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-224700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>232500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-138500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>73500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-369800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-707900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-187700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>197800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>596900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-97300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-121300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>95800</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-36900</v>
+      </c>
+      <c r="E101" s="3">
         <v>26400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-20600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-38300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>11400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>5200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E102" s="3">
         <v>175500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>142400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-210500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>231500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-321100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-335500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-634800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>223200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>285400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>758200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-81400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-146500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>174800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
@@ -656,276 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2031700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2691800</v>
+      </c>
+      <c r="F8" s="3">
         <v>2467800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2778000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2429400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3076300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2709300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2438500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1809300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2347500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1588000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1903800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1808600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1815100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1674700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1233300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1229800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1615900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1643600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1459500</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1551700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2039000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1840400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2080400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1805900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2288700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>2054600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1835800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1354900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1738000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1177400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1333700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1266600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1313200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1187800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>984900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>994700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1232200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1201700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1131700</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>652800</v>
+      </c>
+      <c r="F10" s="3">
         <v>627400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>697600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>623500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>787600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>654700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>602700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>454400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>609500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>410600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>570100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>542000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>501900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>486900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>248400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>235100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>383700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>441900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>327800</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,67 +972,75 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>115300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>122700</v>
+      </c>
+      <c r="F12" s="3">
         <v>114400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>102700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>101700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>121000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>80600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>82100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>84000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>85100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>70600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>68300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>65800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>78900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>66000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>46900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>50500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>64700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>60300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1065,67 +1098,79 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>91</v>
+      <c r="D14" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>116300</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>91</v>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M14" s="3">
         <v>-8600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>4100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>29300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>177100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-40400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1183,8 +1228,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1254,140 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1907600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2513300</v>
+      </c>
+      <c r="F17" s="3">
         <v>2150000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2399200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2147500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2639400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2324500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2092700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1609700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2000900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1402500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1565400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1492100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1566000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1390400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1173800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1357100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1418500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1435600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1349600</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>178500</v>
+      </c>
+      <c r="F18" s="3">
         <v>317800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>378800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>281900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>436900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>384800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>345800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>199600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>346600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>185500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>338400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>316500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>249100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>284300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>59500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-127300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>197400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>208000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1344,303 +1409,335 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-72100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>93900</v>
+      </c>
+      <c r="F20" s="3">
         <v>-158100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>80000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-44100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>59000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-134700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-15100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-45300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>8300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-26300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>101000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>9200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>93200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-86800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-13900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>375500</v>
+      </c>
+      <c r="F21" s="3">
         <v>260200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>554500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>330200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>585900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>326400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>417800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>255800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>375800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>261200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>378000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>391200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>418100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>358100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>217000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-150200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>246700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>265200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>190100</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>43800</v>
+      </c>
+      <c r="F22" s="3">
         <v>44600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>44100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>42100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>38800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>30700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>25300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>14800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>12500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>14200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>13900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>15300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>25200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>25800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>26500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>20400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>20200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>21600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>18600</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>228600</v>
+      </c>
+      <c r="F23" s="3">
         <v>115100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>414700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>195700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>457100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>219400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>319700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>169700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>288800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>179600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>298200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>310100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>324900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>267700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>126200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-234500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>163300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>184200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>114800</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>40400</v>
+      </c>
+      <c r="F24" s="3">
         <v>52000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>76000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>41200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>92000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>77800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>82000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>48700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>79200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>51900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>85300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>65700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>60700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>69000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-8400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>45100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>48900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1698,126 +1795,144 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>188200</v>
+      </c>
+      <c r="F26" s="3">
         <v>63100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>338700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>154500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>365100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>141600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>237700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>121000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>209600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>127700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>212900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>244400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>264200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>198700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>126100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-226100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>118200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>135300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>188500</v>
+      </c>
+      <c r="F27" s="3">
         <v>63000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>337700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>154200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>365300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>141200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>236500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>120900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>209400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>127600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>212600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>244200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>264300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>198800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>126300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-226000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>118400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>135600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1875,8 +1990,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +2055,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1993,8 +2120,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2052,126 +2185,144 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-93900</v>
+      </c>
+      <c r="F32" s="3">
         <v>158100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-80000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>44100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-59000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>134700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>15100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>45300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-8300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>26300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-101000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-93200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>86800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>13900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>188500</v>
+      </c>
+      <c r="F33" s="3">
         <v>63000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>337700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>154200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>365300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>141200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>236500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>120900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>209400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>127600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>212600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>244200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>264300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>198800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>126300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-226000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>118400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>135600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2229,131 +2380,149 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>188500</v>
+      </c>
+      <c r="F35" s="3">
         <v>63000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>337700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>154200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>365300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>141200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>236500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>120900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>209400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>127600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>212600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>244200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>264300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>198800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>126300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-226000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>118400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>135600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2375,8 +2544,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2398,539 +2569,595 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>417400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>491800</v>
+      </c>
+      <c r="F41" s="3">
         <v>283600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>388500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>213000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>202300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>59900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>59100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>55300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>265800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>34300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>355400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>690900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1325700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1309300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1086100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>800700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>42500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>123900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>270400</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>106600</v>
+      </c>
+      <c r="F42" s="3">
         <v>133000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>141100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>125400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>122600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>85500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>114400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>94600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>73600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>74400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>72500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>93300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>76500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>39900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>14800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>13400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>19100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>8500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>568600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>717100</v>
+      </c>
+      <c r="F43" s="3">
         <v>590400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>541200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>650800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>698900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>555300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>410000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>447400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>497300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>496400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>323400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>295700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>339900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>300600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>226900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>310400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>417500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>387100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2195000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2155600</v>
+      </c>
+      <c r="F44" s="3">
         <v>2586200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2352600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2503000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2290100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2474800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2178000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2001500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1691300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1745300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1340600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1276900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1087300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1066500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>916200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1116500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1166300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1252300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1075600</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>57700</v>
+      </c>
+      <c r="F45" s="3">
         <v>59800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>75000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>56600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>66700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>72400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>123000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>168700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>140100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>58500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>44000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>38400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>32900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>31000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>26500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>28800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>26800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>26600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3353100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3528800</v>
+      </c>
+      <c r="F46" s="3">
         <v>3653000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3498400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3548800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3380600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3247900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2884500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2767500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2668100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2408900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2135900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2395200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>2862300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2747300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2270500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2269800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1672200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1798400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1687100</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>68600</v>
+      </c>
+      <c r="F47" s="3">
         <v>86900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>101700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>85900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>90800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>163500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>119300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>127100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>77600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>69400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>59100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>61400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>50400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>43700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>42400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>34000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>32300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>32100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2171000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2098600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2033700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>2047400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1990700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1758500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1621900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1591100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1574600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1407200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1366500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1296200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1278500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1226500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1212300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1229800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1242100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1149000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1088600</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>665500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>665100</v>
+      </c>
+      <c r="F49" s="3">
         <v>735400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>733400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>738700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>741300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>735400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>515200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>505400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>494900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>480300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>466100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>464200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>465100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>460800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>466600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>472600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>610100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>607000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>490400</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2988,8 +3215,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3047,67 +3280,79 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>391400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>339000</v>
+      </c>
+      <c r="F52" s="3">
         <v>315900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>289300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>290900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>261200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>245700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>238400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>219600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>215700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>206800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>225600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>212600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>229600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>245500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>248200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>230600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>210400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>218200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>205200</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3165,67 +3410,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>6642900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>6775500</v>
+      </c>
+      <c r="F54" s="3">
         <v>6889800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>6656500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>6711700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6464600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6151000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>5379300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5210700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5030900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4572600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>4253200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>4429600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>4885900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>4723800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>4240000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4236800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>3767100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3804700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3505300</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3247,8 +3504,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3270,362 +3529,400 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1277900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1450400</v>
+      </c>
+      <c r="F57" s="3">
         <v>1525900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1379500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1603400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1548200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1858400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1571400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1447200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1622900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1419900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1224000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1273200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1296500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1183600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>747800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>957000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1085800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1178200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1028400</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>104400</v>
+      </c>
+      <c r="F58" s="3">
         <v>140000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>136900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>136500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>133100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>450100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>316000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>459900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>132500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>119000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>60400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>54600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>58800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>90800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>59200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>52000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>49500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>48500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>48500</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1107000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>950300</v>
+      </c>
+      <c r="F59" s="3">
         <v>951700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>987700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>912700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>802000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>803900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>795800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1029100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>864000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>617500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>683100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>687900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>837200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>591600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>703700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1455700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>748800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>712100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>656200</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2492500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2505100</v>
+      </c>
+      <c r="F60" s="3">
         <v>2617600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2504100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2652600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2483300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3112400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2683200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2936200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2619400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2156400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1967500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2015700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2192500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1866000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1510700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2464700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1884100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1938800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1733100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2911000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2847000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2963200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2813500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2923800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2883000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2405600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2264800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2060800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2054900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2176600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2203100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2162900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2590700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2695500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2744300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1942400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1836800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1807900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1809000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>585100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>609500</v>
+      </c>
+      <c r="F62" s="3">
         <v>602100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>557400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>557700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>558200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>463200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>422100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>425700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>489400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>466400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>500600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>501500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>577600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>609000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>651000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>623300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>635900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>616400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>577800</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3683,8 +3980,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3742,8 +4045,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3801,67 +4110,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>5994100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5966600</v>
+      </c>
+      <c r="F66" s="3">
         <v>6188200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5880200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6138800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5929700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5984900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5373800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5425600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5166500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4802200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4673900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4683900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5364600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>5174400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4910100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>5034500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4360900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4367500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4124600</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3883,8 +4204,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3942,8 +4265,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -4001,8 +4330,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -4060,8 +4395,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -4119,67 +4460,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>381200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>443100</v>
+      </c>
+      <c r="F72" s="3">
         <v>357000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>443600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>263200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>175500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-129300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-299300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-293600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-404300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-555700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-692000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-551900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-575900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-724400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-932300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-757000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-798800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-851900</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4237,8 +4590,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4296,8 +4655,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4355,67 +4720,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>648800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>808900</v>
+      </c>
+      <c r="F76" s="3">
         <v>701600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>776300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>572900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>534900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>166100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-214900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-135600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-229600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-420700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-254300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-478700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-450600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-670100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-797700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-593800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-562800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-619300</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4473,131 +4850,149 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>188500</v>
+      </c>
+      <c r="F81" s="3">
         <v>63000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>337700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>154200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>365300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>141200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>236500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>120900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>209400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>127600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>212600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>244200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>264300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>198800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>126300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-226000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>118400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>135600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4619,67 +5014,75 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>103700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>103100</v>
+      </c>
+      <c r="F83" s="3">
         <v>100500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>95700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>92400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>90000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>76300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>72800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>71300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>74500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>67400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>65900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>65800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>68000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>64600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>64300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>63900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>63200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>59400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>56700</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4737,8 +5140,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4796,8 +5205,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4855,8 +5270,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4914,8 +5335,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4973,67 +5400,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>141400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>604900</v>
+      </c>
+      <c r="F89" s="3">
         <v>305000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>489400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>258800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>307200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>343300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>332100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-333100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>708800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-265700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>162000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>164900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>318600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>309000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>113900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>212700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>138800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>170500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -5055,67 +5494,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-75200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-227100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-138300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-102600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-117800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-262900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-175500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-112000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-109000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-333000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-135800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-131700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-85500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-107000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-78100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-33300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-34900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-116200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-69300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-56200</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -5173,8 +5620,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5232,67 +5685,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-74100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-222400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-137000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-99900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-115600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-253900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-377000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-115000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-107500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-328900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-130800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-131000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-97000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-119800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-61700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-35200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-43600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-126200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-197400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5314,67 +5779,75 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F96" s="3">
         <v>-13800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-13900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-14200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-12600</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-12600</v>
       </c>
       <c r="I96" s="3">
         <v>-12600</v>
       </c>
       <c r="J96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="L96" s="3">
         <v>-13000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-10700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-10500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-10900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-11000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-9600</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-8900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-8900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5432,8 +5905,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5491,8 +5970,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5550,181 +6035,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-117700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-205100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-236000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-240400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-115300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>109700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>72800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-224700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>232500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-138500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>73500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-369800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-707900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-187700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-23200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>197800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>596900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-97300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-121300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>95800</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-36900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>26400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-17200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-20600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-38300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>11400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-9900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>3300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>5200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>5300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>8900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-7800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>3300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>1700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-74400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>208200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-104900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>175500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>10700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>142400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-210500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>231500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-321100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-335500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-634800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>16400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>223200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>285400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>758200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-81400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-146500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>174800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1841900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2031700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2691800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2467800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2778000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2429400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3076300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2709300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2438500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1809300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2347500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1588000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1903800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1808600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1815100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1674700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1233300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1229800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1615900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1643600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1459500</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1465400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1551700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2039000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1840400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2080400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1805900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2288700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2054600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1835800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1354900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1738000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1177400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1333700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1266600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1313200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1187800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>984900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>994700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1232200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1201700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1131700</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>376500</v>
+      </c>
+      <c r="E10" s="3">
         <v>480000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>652800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>627400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>697600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>623500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>787600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>654700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>602700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>454400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>609500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>410600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>570100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>542000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>501900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>486900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>248400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>235100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>383700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>441900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>327800</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>84400</v>
+      </c>
+      <c r="E12" s="3">
         <v>115300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>122700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>114400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>102700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>101700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>121000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>80600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>82100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>84000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>85100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>70600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>68300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>65800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>78900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>66000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>46900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>50500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>64700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>60300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>55900</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,19 +1121,22 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E14" s="3">
         <v>16200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>116300</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>91</v>
@@ -1124,11 +1144,11 @@
       <c r="H14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>91</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>91</v>
@@ -1136,41 +1156,44 @@
       <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N14" s="3">
         <v>-8600</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>29300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>177100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-40400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1767500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1907600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2513300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2150000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2399200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2147500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2639400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2324500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2092700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1609700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1402500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1565400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1492100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1566000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1390400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1173800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1357100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1418500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1435600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1349600</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E18" s="3">
         <v>124100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>178500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>317800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>378800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>281900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>436900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>384800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>345800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>199600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>346600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>185500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>338400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>316500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>249100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>284300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>59500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-127300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>197400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>208000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,333 +1444,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-72100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>93900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-158100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>80000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-44100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>59000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-134700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-45300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-26300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>101000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>93200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-86800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>169900</v>
+      </c>
+      <c r="E21" s="3">
         <v>155700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>375500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>260200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>554500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>330200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>585900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>326400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>417800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>255800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>375800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>261200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>378000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>391200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>418100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>358100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>217000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-150200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>246700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>265200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>190100</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E22" s="3">
         <v>45000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>43800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>44600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>44100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>42100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>13900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>25200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18600</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E23" s="3">
         <v>7000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>228600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>115100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>414700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>195700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>457100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>219400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>319700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>169700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>288800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>179600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>298200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>310100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>324900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>267700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>126200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-234500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>163300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>184200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>114800</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>40400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>52000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>76000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>41200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>92000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>77800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>82000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>48700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>79200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>51900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>85300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>69000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-8400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>45100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>48900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21500</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>188200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>338700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>154500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>365100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>141600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>237700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>121000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>209600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>127700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>212900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>244400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>264200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>198700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>126100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-226100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>118200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>135300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>188500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>63000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>337700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>154200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>365300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>141200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>236500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>120900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>209400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>127600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>212600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>244200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>264300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>198800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>126300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-226000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>118400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>135600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E32" s="3">
         <v>72100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-93900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>158100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-80000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>44100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-59000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>134700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>45300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>26300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-101000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-93200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>86800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-23500</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>188500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>63000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>337700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>154200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>365300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>141200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>236500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>120900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>209400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>127600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>212600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>244200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>264300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>198800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>126300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-226000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>118400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>135600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>188500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>63000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>337700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>154200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>365300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>141200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>236500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>120900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>209400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>127600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>212600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>244200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>264300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>198800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>126300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-226000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>118400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>135600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2571,593 +2657,621 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E41" s="3">
         <v>417400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>491800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>283600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>388500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>213000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>202300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>265800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>355400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>690900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1325700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1309300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1086100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>800700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>42500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>123900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>270400</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E42" s="3">
         <v>117300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>106600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>133000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>141100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>125400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>122600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>85500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>114400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>94600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>73600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>74400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>93300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>76500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>39900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>8500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>13900</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>499200</v>
+      </c>
+      <c r="E43" s="3">
         <v>568600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>717100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>590400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>541200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>650800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>698900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>555300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>410000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>447400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>497300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>496400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>323400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>295700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>339900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>226900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>310400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>417500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>387100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>2214500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2195000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2155600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2586200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2352600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2503000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2290100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2474800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2178000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2001500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1691300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1745300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1340600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1276900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1087300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1066500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>916200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1116500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1166300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1252300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1075600</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E45" s="3">
         <v>54800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>57700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>59800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>75000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>66700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>123000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>168700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>140100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>58500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>44000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>26600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>3076500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3353100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3528800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3653000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3498400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3548800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3380600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3247900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2884500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2767500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2668100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2408900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2135900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2395200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2862300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2747300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2270500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2269800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1672200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1798400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1687100</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E47" s="3">
         <v>61900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>68600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>86900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>101700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>85900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>90800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>163500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>119300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>127100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>77600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>69400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>59100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>61400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>43700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>42400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>34000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>32300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>32100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>34000</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>2206600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2171000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2174000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2098600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2033700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2047400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1990700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1758500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1621900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1591100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1574600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1407200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1366500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1296200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1278500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1226500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1212300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1229800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1242100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1149000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1088600</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>663100</v>
+      </c>
+      <c r="E49" s="3">
         <v>665500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>665100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>735400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>733400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>738700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>741300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>735400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>515200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>505400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>494900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>480300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>466100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>464200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>465100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>460800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>466600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>472600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>610100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>607000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>490400</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3286,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>377200</v>
+      </c>
+      <c r="E52" s="3">
         <v>391400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>339000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>315900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>289300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>290900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>261200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>245700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>238400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>219600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>215700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>206800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>225600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>212600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>229600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>245500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>248200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>230600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>210400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>218200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>205200</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>6378400</v>
+      </c>
+      <c r="E54" s="3">
         <v>6642900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6775500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6889800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6656500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6711700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6464600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6151000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5379300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5210700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5030900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4572600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4253200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4429600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4885900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4723800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4240000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4236800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3767100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3804700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3505300</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3531,398 +3661,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1225300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1277900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1450400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1525900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1379500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1603400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1548200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1858400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1571400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1447200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1622900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1419900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1224000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1273200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1296500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1183600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>747800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>957000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1085800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1178200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1028400</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E58" s="3">
         <v>107600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>104400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>140000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>136900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>136500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>133100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>450100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>316000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>459900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>132500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>119000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>60400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>54600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>58800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>90800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>59200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>52000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>49500</v>
-      </c>
-      <c r="V58" s="3">
-        <v>48500</v>
       </c>
       <c r="W58" s="3">
         <v>48500</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>998600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1107000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>950300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>951700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>987700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>912700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>802000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>803900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>795800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1029100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>864000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>617500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>683100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>687900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>837200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>591600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>703700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1455700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>748800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>712100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>656200</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2333900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2492500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2505100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2617600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2504100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2652600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2483300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3112400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2683200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2936200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2619400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2156400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1967500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2015700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2192500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1866000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1510700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2464700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1884100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1938800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1733100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2914000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2911000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2847000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2963200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2813500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2923800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2883000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2405600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2264800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2060800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2054900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2176600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2203100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2162900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2590700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2695500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2744300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1942400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1836800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1807900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1809000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>576400</v>
+      </c>
+      <c r="E62" s="3">
         <v>585100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>609500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>602100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>557400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>557700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>558200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>463200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>422100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>425700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>489400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>466400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>500600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>501500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>577600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>609000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>651000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>623300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>635900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>616400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>577800</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>5830700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5994100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5966600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6188200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5880200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6138800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5929700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5984900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5373800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5425600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5166500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4802200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4673900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4683900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5364600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5174400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4910100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5034500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4360900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4367500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4124600</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>210700</v>
+      </c>
+      <c r="E72" s="3">
         <v>381200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>443100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>357000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>443600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>263200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>175500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-129300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-299300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-293600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-404300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-555700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-692000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-551900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-575900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-724400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-932300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1033900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-757000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-798800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-851900</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>547700</v>
+      </c>
+      <c r="E76" s="3">
         <v>648800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>808900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>701600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>776300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>572900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>534900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>166100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-214900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-135600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-229600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-420700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-254300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-478700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-450600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-670100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-797700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-593800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-562800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-619300</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>188500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>63000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>337700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>154200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>365300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>141200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>236500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>120900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>209400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>127600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>212600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>244200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>264300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>198800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>126300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-226000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>118400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>135600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E83" s="3">
         <v>103700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>103100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>95700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>92400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>90000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>76300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>71300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>74500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>65800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>68000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>64600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>63900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>63200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>59400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>56700</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E89" s="3">
         <v>141400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>604900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>305000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>489400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>258800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>307200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>343300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>332100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-333100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>708800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-265700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>162000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>164900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>318600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>309000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>113900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>212700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>138800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>170500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-105600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-75200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-227100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-138300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-102600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-117800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-262900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-175500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-112000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-109000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-333000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-135800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-131700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-85500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-107000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-78100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-34900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-116200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-69300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-56200</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-106600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-74100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-222400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-137000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-99900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-115600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-253900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-377000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-107500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-328900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-130800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-131000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-97000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-119800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-43600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-126200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-197400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-67500</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5781,28 +6014,29 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E96" s="3">
         <v>-15800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-13700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-13800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-13900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-14200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-12600</v>
       </c>
       <c r="J96" s="3">
         <v>-12600</v>
@@ -5811,26 +6045,26 @@
         <v>-12600</v>
       </c>
       <c r="L96" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="M96" s="3">
         <v>-13000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-10700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-10500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-10900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-9600</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -5838,16 +6072,19 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
-        <v>-8900</v>
+        <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>-8900</v>
       </c>
       <c r="W96" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="X96" s="3">
         <v>-9700</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-261100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-117700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-205100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-236000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-240400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-115300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>109700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>72800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-224700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>232500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-138500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>73500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-369800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-707900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-187700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-23200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>197800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>596900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-97300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-121300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>95800</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>30800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-36900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>26400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-38300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>5300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-74400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>208200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-104900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>175500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>142400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-210500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>231500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-321100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-335500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-634800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>223200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>285400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>758200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-81400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-146500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>174800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DOO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>DOO</t>
   </si>
@@ -656,148 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="F7" s="2">
         <v>45961</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45869</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45777</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45688</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45596</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45504</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45412</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45322</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1757100</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
         <v>1605800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1364400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1336600</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
         <v>1416200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1311100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1455100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1344500</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
         <v>1219600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1077000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1050900</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3">
         <v>1104000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1022100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1075500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>412600</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
         <v>386200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>287400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>285700</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3">
         <v>312200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>289100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>379600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,37 +834,45 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3">
         <v>78600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>69700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>76000</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3">
         <v>68700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>57500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>78700</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,66 +900,84 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
-        <v>400</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>15300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>6500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>10300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F15" s="3">
         <v>84100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>81700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>77100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>14200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>78500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>77500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>75500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +986,80 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1595500</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="3">
         <v>1460600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1298500</v>
       </c>
-      <c r="F17" s="3">
-        <v>1263500</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H17" s="3">
+        <v>1263800</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="3">
         <v>1302600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1217200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1306800</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>161600</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3">
         <v>145100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>65800</v>
       </c>
-      <c r="F18" s="3">
-        <v>73100</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H18" s="3">
+        <v>72700</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="3">
         <v>113600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>94000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>148300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,153 +1071,185 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
         <v>35400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>9000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-83900</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>19200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>11400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>53300</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>235200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>15500</v>
+      </c>
+      <c r="F21" s="3">
         <v>193800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>138500</v>
       </c>
-      <c r="F21" s="3">
-        <v>234000</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>233700</v>
+      </c>
+      <c r="I21" s="3">
         <v>14200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>172900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>160000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>170500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3">
         <v>36000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>32400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>30900</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3">
         <v>34300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>33400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>32700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3">
         <v>76400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>26200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>126600</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="3">
         <v>45700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>45500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>53300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3">
         <v>21800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-15000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>10100</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3">
         <v>23800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>15100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>22400</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1277,84 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>93500</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3">
         <v>54600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>41300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>116500</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="3">
         <v>22000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>30400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>30900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3">
         <v>49300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>17600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>108700</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J27" s="3">
         <v>5100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5500</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,37 +1382,49 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-5500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-24300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>-7900</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-17100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-25200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-36300</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1452,14 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1487,84 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
         <v>-35400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-9000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>83900</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>-19200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-11400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-53300</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3">
         <v>49300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>17600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>108700</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J33" s="3">
         <v>5100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5500</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1592,89 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3">
         <v>49300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>17600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>108700</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J35" s="3">
         <v>5100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5500</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="F38" s="2">
         <v>45961</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45869</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45777</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45688</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45596</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45504</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45412</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45322</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1686,10 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1701,45 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>511900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>314900</v>
+      </c>
+      <c r="F41" s="3">
         <v>178500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>196200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>227300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>124900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>105500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>119700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>303700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>367600</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,124 +1767,154 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>499000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>563800</v>
+      </c>
+      <c r="F43" s="3">
         <v>570500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>502800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>493100</v>
       </c>
-      <c r="G43" s="3">
-        <v>523900</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>534700</v>
+      </c>
+      <c r="J43" s="3">
         <v>422500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>361400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>413700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>536000</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1368900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1345200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1402100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1297700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1307400</v>
       </c>
-      <c r="G44" s="3">
-        <v>1195500</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>1225800</v>
+      </c>
+      <c r="J44" s="3">
         <v>1434000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1603200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1597100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1611200</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>186500</v>
+      </c>
+      <c r="F45" s="3">
         <v>168500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>202500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>284200</v>
       </c>
-      <c r="G45" s="3">
-        <v>349400</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>303100</v>
+      </c>
+      <c r="J45" s="3">
         <v>498300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>142900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>125200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>122800</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2569500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2410400</v>
+      </c>
+      <c r="F46" s="3">
         <v>2319600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2199300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2312000</v>
       </c>
-      <c r="G46" s="3">
-        <v>2193600</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>2188500</v>
+      </c>
+      <c r="J46" s="3">
         <v>2460400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2227200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2439700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2637600</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1733,66 +1942,84 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1635000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1495900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1512900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1540800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1524600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1465900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1496200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1597400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1579600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1624900</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>365400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>364900</v>
+      </c>
+      <c r="F49" s="3">
         <v>449100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>453300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>438100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>417200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>434500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>480000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>484200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>497100</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +2047,14 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +2082,49 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>68700</v>
+      </c>
+      <c r="F52" s="3">
         <v>55000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>37600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>45100</v>
       </c>
-      <c r="G52" s="3">
-        <v>38000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>37900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K52" s="3">
         <v>43700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>46000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>52400</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2152,49 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4956100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4661400</v>
+      </c>
+      <c r="F54" s="3">
         <v>4646400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4544900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4589700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4348300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4669200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>4617600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>4833300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5064300</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2206,10 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2221,220 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1148500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>733200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1153600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>887400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>933600</v>
       </c>
-      <c r="G57" s="3">
-        <v>573100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>579500</v>
+      </c>
+      <c r="J57" s="3">
         <v>961100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>887000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>929800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>767500</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>76900</v>
+      </c>
+      <c r="F58" s="3">
         <v>74900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>73600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>75800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>69700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>87500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>79600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>78300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>78000</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>735000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>681000</v>
+      </c>
+      <c r="F59" s="3">
         <v>659200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>676900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>713800</v>
       </c>
-      <c r="G59" s="3">
-        <v>763100</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>747700</v>
+      </c>
+      <c r="J59" s="3">
         <v>749200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>722900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>805400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>710300</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1980100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1894600</v>
+      </c>
+      <c r="F60" s="3">
         <v>1887600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1637900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1723200</v>
       </c>
-      <c r="G60" s="3">
-        <v>1677200</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>1668200</v>
+      </c>
+      <c r="J60" s="3">
         <v>1797800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1689600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1813500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1872400</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2069600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1898700</v>
+      </c>
+      <c r="F61" s="3">
         <v>1913300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2119700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2103700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2093200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2097700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2109600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2118000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2128000</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>176300</v>
+      </c>
+      <c r="F62" s="3">
         <v>182200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>185600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>172500</v>
       </c>
-      <c r="G62" s="3">
-        <v>174500</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>175900</v>
+      </c>
+      <c r="J62" s="3">
         <v>160600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>169600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>175600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>175000</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2462,14 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2497,14 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2532,49 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4440000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4211200</v>
+      </c>
+      <c r="F66" s="3">
         <v>4234800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4188200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4250000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4177800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4284200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4216400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4357200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4456000</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2586,10 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2617,14 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2652,14 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2687,14 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2722,49 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>113400</v>
+      </c>
+      <c r="F72" s="3">
         <v>120100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>31600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>72300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-25800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>146200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>152500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>277400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2792,14 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2827,14 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2862,49 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>511700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>445400</v>
+      </c>
+      <c r="F76" s="3">
         <v>406000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>350900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>335900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>166700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>380800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>396500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>472100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>604600</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2932,89 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46142</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="F80" s="2">
         <v>45961</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45869</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45777</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45688</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45596</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45504</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45412</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45322</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3">
         <v>49300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>17600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>108700</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J81" s="3">
         <v>5100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5500</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +3026,45 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>78500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>76400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>74400</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>72400</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L83" s="3">
         <v>66300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +3092,14 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +3127,14 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +3162,14 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +3197,14 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3232,49 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>312600</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
         <v>293400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>114600</v>
       </c>
-      <c r="F89" s="3">
-        <v>155200</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H89" s="3">
+        <v>185100</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J89" s="3">
         <v>122400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>65600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>102900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3286,45 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3">
         <v>-51400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-50900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-32600</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J91" s="3">
         <v>-81600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-71300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-48600</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3352,14 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3387,49 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>-55500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-48900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-37200</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="3">
         <v>-85200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-77200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-53900</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3441,45 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>11300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>11300</v>
+        <v>13400</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
         <v>11300</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
+      <c r="G96" s="3">
+        <v>11300</v>
       </c>
       <c r="H96" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3">
         <v>11100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>11100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>11500</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3507,14 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3542,14 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,91 +3577,115 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
         <v>-256800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-68700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-57100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J100" s="3">
         <v>-46100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-189000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-85600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3">
         <v>-5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>18200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-17500</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3">
         <v>-26600</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L101" s="3">
         <v>-12700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-15400</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>198100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-15300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-29400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>95700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-14100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-182400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-54100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>
